--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-06T07:18:32.670Z</t>
+    <t>2026-08-06T10:32:06.579Z</t>
   </si>
   <si>
     <t>Merkle - We Power the Experience Economy</t>
